--- a/tests/workbooktests/workbooks/test_calibrationhelpers.xlsx
+++ b/tests/workbooktests/workbooks/test_calibrationhelpers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729A553B-4090-4776-AEC7-2C5BB5170DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B723D96A-22E1-4A3B-94CC-5220F3F2A5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13905" yWindow="-20130" windowWidth="21330" windowHeight="15900" xr2:uid="{F8183AC6-1ED6-4E47-A659-19168C9694C8}"/>
+    <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" xr2:uid="{F8183AC6-1ED6-4E47-A659-19168C9694C8}"/>
   </bookViews>
   <sheets>
     <sheet name="qlSwaptionHelper" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -261,7 +261,7 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -273,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -639,27 +639,27 @@
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R4C2YieldTermStructureHandle,A</v>
+      <c r="B4" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.02)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
+      <c r="B5" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlFlatForward(B2,0.02)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -686,13 +686,13 @@
       <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="8">
-        <f>B2+365</f>
-        <v>46539</v>
-      </c>
-      <c r="E8" s="8">
-        <f>B2+365</f>
-        <v>46539</v>
+      <c r="D8" s="8" t="e">
+        <f ca="1">B2+365</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" s="8" t="e">
+        <f ca="1">B2+365</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -708,9 +708,9 @@
       <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="8">
-        <f>E8+730</f>
-        <v>47269</v>
+      <c r="E9" s="8" t="e">
+        <f ca="1">E8+730</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -734,21 +734,21 @@
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlEuribor("6M",$B$4)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R11C2Euribor,A</v>
-      </c>
-      <c r="C11" s="4" t="str" cm="1">
-        <f t="array" ref="C11">_xll.qlEuribor("6M",B4)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R11C3Euribor,A</v>
-      </c>
-      <c r="D11" s="4" t="str" cm="1">
-        <f t="array" ref="D11">_xll.qlEuribor("6M",$B$4)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R11C4Euribor,A</v>
-      </c>
-      <c r="E11" s="4" t="str" cm="1">
-        <f t="array" ref="E11">_xll.qlEuribor("6M",$B$4)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R11C5Euribor,A</v>
+      <c r="B11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlEuribor("6M",$B$4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">_xll.qlEuribor("6M",B4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1">_xll.qlEuribor("6M",$B$4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="E11" ca="1">_xll.qlEuribor("6M",$B$4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -806,21 +806,21 @@
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="4" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C15" s="4" t="str">
-        <f>B5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="D15" s="4" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="E15" s="4" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
+      <c r="B15" s="4" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" s="4" t="e">
+        <f ca="1">B5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" s="4" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="4" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -901,126 +901,126 @@
       <c r="E22" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" t="str" cm="1">
-        <f t="array" ref="B24">_xll.qlSwaptionHelper(B8,B9,B10,B11,B12,B13,B14,B15)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R24C2SwaptionHelper,A</v>
-      </c>
-      <c r="C24" t="str" cm="1">
-        <f t="array" ref="C24">_xll.qlSwaptionHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R24C3SwaptionHelper,A</v>
-      </c>
-      <c r="D24" t="str" cm="1">
-        <f t="array" ref="D24">_xll.qlSwaptionHelper(D8,D9,D10,D11,D12,D13,D14,D15)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R24C4SwaptionHelper,A</v>
-      </c>
-      <c r="E24" t="str" cm="1">
-        <f t="array" ref="E24">_xll.qlSwaptionHelper(E8,E9,E10,E11,E12,E13,E14,E15)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet1!R24C5SwaptionHelper,A</v>
+      <c r="B24" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlSwaptionHelper(B8,B9,B10,B11,B12,B13,B14,B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C24" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlSwaptionHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D24" t="e" cm="1">
+        <f t="array" aca="1" ref="D24" ca="1">_xll.qlSwaptionHelper(D8,D9,D10,D11,D12,D13,D14,D15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E24" t="e" cm="1">
+        <f t="array" aca="1" ref="E24" ca="1">_xll.qlSwaptionHelper(E8,E9,E10,E11,E12,E13,E14,E15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" cm="1">
-        <f t="array" ref="B26">_xll.qlBlackCalibrationHelperMarketValue(B24)</f>
-        <v>9.1854188200250798E-3</v>
-      </c>
-      <c r="C26" cm="1">
-        <f t="array" ref="C26">_xll.qlBlackCalibrationHelperMarketValue(C24)</f>
-        <v>0.5687196556581241</v>
-      </c>
-      <c r="D26" cm="1">
-        <f t="array" ref="D26">_xll.qlBlackCalibrationHelperMarketValue(D24)</f>
-        <v>9.1854188200250798E-3</v>
-      </c>
-      <c r="E26" cm="1">
-        <f t="array" ref="E26">_xll.qlBlackCalibrationHelperMarketValue(E24)</f>
-        <v>9.1360994073147565E-3</v>
+      <c r="B26" t="e" cm="1">
+        <f t="array" aca="1" ref="B26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(B24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C26" t="e" cm="1">
+        <f t="array" aca="1" ref="C26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(C24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D26" t="e" cm="1">
+        <f t="array" aca="1" ref="D26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(D24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E26" t="e" cm="1">
+        <f t="array" aca="1" ref="E26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(E24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="1" cm="1">
-        <f t="array" ref="B27">_xll.qlBlackCalibrationHelperImpliedVolatility(B24,B26)</f>
-        <v>0.4</v>
-      </c>
-      <c r="C27" s="2" cm="1">
-        <f t="array" ref="C27">_xll.qlBlackCalibrationHelperImpliedVolatility(C24,C26)</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="D27" s="2" cm="1">
-        <f t="array" ref="D27">_xll.qlBlackCalibrationHelperImpliedVolatility(D24,D26)</f>
-        <v>0.4</v>
-      </c>
-      <c r="E27" s="2" cm="1">
-        <f t="array" ref="E27">_xll.qlBlackCalibrationHelperImpliedVolatility(E24,E26)</f>
-        <v>0.4</v>
+      <c r="B27" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(B24,B26)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C27" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(C24,C26)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D27" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(D24,D26)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E27" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="E27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(E24,E26)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
-      <c r="B28" cm="1">
-        <f t="array" ref="B28">_xll.qlBlackCalibrationHelperBlackPrice(B24,B27)</f>
-        <v>9.1854188200250798E-3</v>
-      </c>
-      <c r="C28" cm="1">
-        <f t="array" ref="C28">_xll.qlBlackCalibrationHelperBlackPrice(C24,C27)</f>
-        <v>0.5687196556581241</v>
-      </c>
-      <c r="D28" cm="1">
-        <f t="array" ref="D28">_xll.qlBlackCalibrationHelperBlackPrice(D24,D27)</f>
-        <v>9.1854188200250798E-3</v>
-      </c>
-      <c r="E28" cm="1">
-        <f t="array" ref="E28">_xll.qlBlackCalibrationHelperBlackPrice(E24,E27)</f>
-        <v>9.1360994073147565E-3</v>
+      <c r="B28" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(B24,B27)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C28" t="e" cm="1">
+        <f t="array" aca="1" ref="C28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(C24,C27)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D28" t="e" cm="1">
+        <f t="array" aca="1" ref="D28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(D24,D27)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E28" t="e" cm="1">
+        <f t="array" aca="1" ref="E28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(E24,E27)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="1" cm="1">
-        <f t="array" ref="B29">_xll.qlBlackCalibrationHelperVolatility(B24)</f>
-        <v>0.4</v>
-      </c>
-      <c r="C29" s="2" cm="1">
-        <f t="array" ref="C29">_xll.qlBlackCalibrationHelperVolatility(C24)</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="D29" s="2" cm="1">
-        <f t="array" ref="D29">_xll.qlBlackCalibrationHelperVolatility(D24)</f>
-        <v>0.4</v>
-      </c>
-      <c r="E29" s="2" cm="1">
-        <f t="array" ref="E29">_xll.qlBlackCalibrationHelperVolatility(E24)</f>
-        <v>0.4</v>
+      <c r="B29" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlBlackCalibrationHelperVolatility(B24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C29" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="C29" ca="1">_xll.qlBlackCalibrationHelperVolatility(C24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D29" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="D29" ca="1">_xll.qlBlackCalibrationHelperVolatility(D24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E29" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="E29" ca="1">_xll.qlBlackCalibrationHelperVolatility(E24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="str" cm="1">
-        <f t="array" ref="B30">_xll.qlBlackCalibrationHelperVolatilityType(B24)</f>
-        <v>SHIFTEDLOGNORMAL</v>
-      </c>
-      <c r="C30" t="str" cm="1">
-        <f t="array" ref="C30">_xll.qlBlackCalibrationHelperVolatilityType(C24)</f>
-        <v>NORMAL</v>
-      </c>
-      <c r="D30" t="str" cm="1">
-        <f t="array" ref="D30">_xll.qlBlackCalibrationHelperVolatilityType(D24)</f>
-        <v>SHIFTEDLOGNORMAL</v>
-      </c>
-      <c r="E30" t="str" cm="1">
-        <f t="array" ref="E30">_xll.qlBlackCalibrationHelperVolatilityType(E24)</f>
-        <v>SHIFTEDLOGNORMAL</v>
+      <c r="B30" t="e" cm="1">
+        <f t="array" aca="1" ref="B30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(B24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C30" t="e" cm="1">
+        <f t="array" aca="1" ref="C30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(C24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D30" t="e" cm="1">
+        <f t="array" aca="1" ref="D30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(D24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E30" t="e" cm="1">
+        <f t="array" aca="1" ref="E30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(E24)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1050,27 +1050,27 @@
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R4C2YieldTermStructureHandle,A</v>
+      <c r="B4" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.02)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R5C2YieldTermStructureHandle,A</v>
+      <c r="B5" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlFlatForward(B2,0.02)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1131,13 +1131,13 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="str" cm="1">
-        <f t="array" ref="B10">_xll.qlEuribor("6m",$B$4)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R10C2Euribor,A</v>
-      </c>
-      <c r="C10" s="4" t="str" cm="1">
-        <f t="array" ref="C10">_xll.qlEuribor("6m",$B$4)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R10C3Euribor,A</v>
+      <c r="B10" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlEuribor("6m",$B$4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_xll.qlEuribor("6m",$B$4)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D10" t="s">
         <v>1</v>
@@ -1225,13 +1225,13 @@
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R5C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C14" s="4" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R5C2YieldTermStructureHandle,A</v>
+      <c r="B14" s="4" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" s="4" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D14" t="s">
         <v>1</v>
@@ -1310,78 +1310,78 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B19" t="str" cm="1">
-        <f t="array" ref="B19">_xll.qlCapHelper(B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R19C2CapHelper,A</v>
-      </c>
-      <c r="C19" t="str" cm="1">
-        <f t="array" ref="C19">_xll.qlCapHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet2!R19C3CapHelper,A</v>
+      <c r="B19" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlCapHelper(B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" t="e" cm="1">
+        <f t="array" aca="1" ref="C19" ca="1">_xll.qlCapHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" cm="1">
-        <f t="array" ref="B21">_xll.qlBlackCalibrationHelperMarketValue(B19)</f>
-        <v>2.5622813960893911E-2</v>
-      </c>
-      <c r="C21" cm="1">
-        <f t="array" ref="C21">_xll.qlBlackCalibrationHelperMarketValue(C19)</f>
-        <v>1.9464920445835268E-2</v>
+      <c r="B21" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlBlackCalibrationHelperMarketValue(B19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C21" t="e" cm="1">
+        <f t="array" aca="1" ref="C21" ca="1">_xll.qlBlackCalibrationHelperMarketValue(C19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="1" cm="1">
-        <f t="array" ref="B22">_xll.qlBlackCalibrationHelperImpliedVolatility(B19,B21)</f>
-        <v>0.35</v>
-      </c>
-      <c r="C22" s="1" cm="1">
-        <f t="array" ref="C22">_xll.qlBlackCalibrationHelperImpliedVolatility(C19,C21)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B22" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(B19,B21)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C22" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C22" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(C19,C21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" cm="1">
-        <f t="array" ref="B23">_xll.qlBlackCalibrationHelperBlackPrice(B19,B22)</f>
-        <v>2.5622813960893911E-2</v>
-      </c>
-      <c r="C23" cm="1">
-        <f t="array" ref="C23">_xll.qlBlackCalibrationHelperBlackPrice(C19,C22)</f>
-        <v>1.9464920445835268E-2</v>
+      <c r="B23" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(B19,B22)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C23" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(C19,C22)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="1" cm="1">
-        <f t="array" ref="B24">_xll.qlBlackCalibrationHelperVolatility(B19)</f>
-        <v>0.35</v>
-      </c>
-      <c r="C24" s="1" cm="1">
-        <f t="array" ref="C24">_xll.qlBlackCalibrationHelperVolatility(C19)</f>
-        <v>8.0000000000000002E-3</v>
+      <c r="B24" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBlackCalibrationHelperVolatility(B19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C24" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlBlackCalibrationHelperVolatility(C19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="4" t="str" cm="1">
-        <f t="array" ref="B25">_xll.qlBlackCalibrationHelperVolatilityType(B19)</f>
-        <v>SHIFTEDLOGNORMAL</v>
-      </c>
-      <c r="C25" s="4" t="str" cm="1">
-        <f t="array" ref="C25">_xll.qlBlackCalibrationHelperVolatilityType(C19)</f>
-        <v>NORMAL</v>
+      <c r="B25" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(B19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C25" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C25" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(C19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1411,27 +1411,27 @@
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R4C2YieldTermStructureHandle,A</v>
+      <c r="B4" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.02)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R5C2YieldTermStructureHandle,A</v>
+      <c r="B5" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlFlatForward(B2,0.02)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1561,13 +1561,13 @@
       <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="str">
-        <f>$B$4</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R4C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C13" t="str">
-        <f>$B$4</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R4C2YieldTermStructureHandle,A</v>
+      <c r="B13" t="e">
+        <f ca="1">$B$4</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" t="e">
+        <f ca="1">$B$4</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -1586,13 +1586,13 @@
       <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R5C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C14" t="str">
-        <f>$B$5</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R5C2YieldTermStructureHandle,A</v>
+      <c r="B14" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" t="e">
+        <f ca="1">$B$5</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1628,78 +1628,78 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B17" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlHestonModelHelper(B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R17C2HestonModelHelper,A</v>
-      </c>
-      <c r="C17" t="str" cm="1">
-        <f t="array" ref="C17">_xll.qlHestonModelHelper(C8,C9,C10,C11,C12,C13,C14,C15)</f>
-        <v>⚡[test_calibrationhelpers.xlsx]Sheet3!R17C3HestonModelHelper,A</v>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlHestonModelHelper(B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" t="e" cm="1">
+        <f t="array" aca="1" ref="C17" ca="1">_xll.qlHestonModelHelper(C8,C9,C10,C11,C12,C13,C14,C15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" cm="1">
-        <f t="array" ref="B19">_xll.qlBlackCalibrationHelperMarketValue(B17)</f>
-        <v>12.424776089141019</v>
-      </c>
-      <c r="C19" cm="1">
-        <f t="array" ref="C19">_xll.qlBlackCalibrationHelperMarketValue(C17)</f>
-        <v>12.424776089141019</v>
+      <c r="B19" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlBlackCalibrationHelperMarketValue(B17)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" t="e" cm="1">
+        <f t="array" aca="1" ref="C19" ca="1">_xll.qlBlackCalibrationHelperMarketValue(C17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="1" cm="1">
-        <f t="array" ref="B20">_xll.qlBlackCalibrationHelperImpliedVolatility(B17,B19)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C20" s="1" cm="1">
-        <f t="array" ref="C20">_xll.qlBlackCalibrationHelperImpliedVolatility(C17,C19)</f>
-        <v>0.25</v>
+      <c r="B20" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(B17,B19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C20" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C20" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(C17,C19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
-      <c r="B21" cm="1">
-        <f t="array" ref="B21">_xll.qlBlackCalibrationHelperBlackPrice(B17,B20)</f>
-        <v>12.424776089141019</v>
-      </c>
-      <c r="C21" cm="1">
-        <f t="array" ref="C21">_xll.qlBlackCalibrationHelperBlackPrice(C17,C20)</f>
-        <v>12.424776089141019</v>
+      <c r="B21" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(B17,B20)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C21" t="e" cm="1">
+        <f t="array" aca="1" ref="C21" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(C17,C20)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="1" cm="1">
-        <f t="array" ref="B22">_xll.qlBlackCalibrationHelperVolatility(B17)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C22" s="1" cm="1">
-        <f t="array" ref="C22">_xll.qlBlackCalibrationHelperVolatility(C17)</f>
-        <v>0.25</v>
+      <c r="B22" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackCalibrationHelperVolatility(B17)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C22" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C22" ca="1">_xll.qlBlackCalibrationHelperVolatility(C17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="4" t="str" cm="1">
-        <f t="array" ref="B23">_xll.qlBlackCalibrationHelperVolatilityType(B17)</f>
-        <v>SHIFTEDLOGNORMAL</v>
-      </c>
-      <c r="C23" s="4" t="str" cm="1">
-        <f t="array" ref="C23">_xll.qlBlackCalibrationHelperVolatilityType(C17)</f>
-        <v>SHIFTEDLOGNORMAL</v>
+      <c r="B23" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(B17)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C23" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(C17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
